--- a/tests/workbooks/test_optimizers.xlsx
+++ b/tests/workbooks/test_optimizers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8ED92A-48CE-486D-8593-7CEA69F0EFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52281D79-9129-4901-99CF-F7A11B5E3468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13905" yWindow="-20130" windowWidth="21330" windowHeight="15900" activeTab="1" xr2:uid="{E76B3670-D287-482D-903A-DB7A1E5EF242}"/>
+    <workbookView xWindow="14340" yWindow="-19695" windowWidth="21330" windowHeight="15900" activeTab="1" xr2:uid="{E76B3670-D287-482D-903A-DB7A1E5EF242}"/>
   </bookViews>
   <sheets>
     <sheet name="Constraints" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>qlNoConstraint</t>
   </si>
@@ -143,6 +143,33 @@
   </si>
   <si>
     <t>qlEndCriteriaSucceded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    epsfcn: float = 1.0e-8,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    xtol: float = 1.0e-8,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    gtol: float = 1.0e-8,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    use_cost_functions_jacobian: bool = False,</t>
+  </si>
+  <si>
+    <t>epsfcn</t>
+  </si>
+  <si>
+    <t>xtol</t>
+  </si>
+  <si>
+    <t>gtol</t>
+  </si>
+  <si>
+    <t>use_cost_functions_jacobian</t>
+  </si>
+  <si>
+    <t>qlLevenbergMarquardt</t>
   </si>
 </sst>
 </file>
@@ -606,7 +633,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{394B9001-4C2C-46EE-A1BD-66EDDB727756}">
-  <dimension ref="A2:D17"/>
+  <dimension ref="A2:E25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.33203125" customWidth="1"/>
@@ -738,13 +765,75 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
       <c r="B17" t="b" cm="1">
         <f t="array" ref="B17">_xll.qlEndCriteriaSucceded($B$8,A17)</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="1">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="1">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="1">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" t="str" cm="1">
+        <f t="array" ref="B24">_xll.qlLevenbergMarquardt()</f>
+        <v>⚡[test_optimizers.xlsx]EndCriteria!R24C2LevenbergMarquardt,A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" t="str" cm="1">
+        <f t="array" ref="B25">_xll.qlLevenbergMarquardt(B19,B20,B21,B22)</f>
+        <v>⚡[test_optimizers.xlsx]EndCriteria!R25C2LevenbergMarquardt,A</v>
       </c>
     </row>
   </sheetData>
